--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +253,8 @@
     <t>Code définissant l'activité de soins autorisée -AS- (article L.6122-1 du CSP)</t>
   </si>
   <si>
-    <t>Synonyme MOS : activite ; la liste des activités de soins soumises à autorisation est fixée par décret en Conseil d'Etat (article L.6122-25 du CSP).</t>
+    <t>Synonyme : activite 
+ la liste des activités de soins soumises à autorisation est fixée par décret en Conseil d'Etat (article L.6122-25 du CSP).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-healthcareservice-activity-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
